--- a/data/chapter19_lowlevel_function.xlsx
+++ b/data/chapter19_lowlevel_function.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kyowapharma-my.sharepoint.com/personal/araya-t_kyowayakuhin_co_jp/Documents/R_scripts/R入門/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{E54D0200-F7C1-4F15-9111-087A81B57FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE416C63-C1DF-4754-B2CD-58E49A6165D0}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95CA4FA-FE03-4D87-9BA2-92A87C0B3932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19320" windowHeight="12960" activeTab="1" xr2:uid="{3CCFC38F-EA28-42DC-A287-D1AB373169F7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" activeTab="1" xr2:uid="{3CCFC38F-EA28-42DC-A287-D1AB373169F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1668,14 +1663,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1713,7 +1704,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1819,7 +1810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1961,7 +1952,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1970,13 +1961,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52CB9DFC-3E25-4A04-A48A-9438F94DBD5E}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30.296875" customWidth="1"/>
-    <col min="2" max="2" width="49.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.25" customWidth="1"/>
+    <col min="2" max="2" width="49.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>192</v>
       </c>
@@ -1984,7 +1975,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>194</v>
       </c>
@@ -1992,7 +1983,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>195</v>
       </c>
@@ -2000,7 +1991,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>207</v>
       </c>
@@ -2008,7 +1999,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>196</v>
       </c>
@@ -2016,7 +2007,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -2024,7 +2015,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>198</v>
       </c>
@@ -2032,7 +2023,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>199</v>
       </c>
@@ -2040,7 +2031,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>200</v>
       </c>
@@ -2048,7 +2039,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -2056,7 +2047,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>202</v>
       </c>
@@ -2064,7 +2055,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>203</v>
       </c>
@@ -2072,7 +2063,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>204</v>
       </c>
@@ -2080,7 +2071,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>205</v>
       </c>
@@ -2091,21 +2082,22 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44520B7A-A80C-4D49-9F2D-29F2491764F1}">
   <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2119,7 +2111,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2133,7 +2125,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2147,7 +2139,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2161,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2175,7 +2167,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2189,7 +2181,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2203,7 +2195,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2217,7 +2209,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2231,7 +2223,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2245,7 +2237,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2259,7 +2251,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2273,7 +2265,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2287,7 +2279,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2301,7 +2293,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2315,7 +2307,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2329,7 +2321,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2343,7 +2335,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2357,7 +2349,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2371,7 +2363,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2385,7 +2377,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2399,7 +2391,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2413,7 +2405,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2427,7 +2419,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2441,7 +2433,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2455,7 +2447,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2469,7 +2461,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2483,7 +2475,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2497,7 +2489,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2511,7 +2503,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2525,7 +2517,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2539,7 +2531,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2553,7 +2545,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2567,7 +2559,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2581,7 +2573,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2595,7 +2587,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2609,7 +2601,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2623,7 +2615,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2637,7 +2629,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2651,7 +2643,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2665,7 +2657,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2679,7 +2671,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2693,7 +2685,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2707,7 +2699,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2721,7 +2713,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2735,7 +2727,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -2749,7 +2741,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2763,7 +2755,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -2777,7 +2769,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -2791,7 +2783,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2805,7 +2797,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -2819,7 +2811,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2833,7 +2825,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -2847,7 +2839,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -2861,7 +2853,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2875,7 +2867,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -2889,7 +2881,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -2903,7 +2895,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>181</v>
       </c>
@@ -2917,7 +2909,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -2931,7 +2923,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2945,7 +2937,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -2959,7 +2951,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -2976,5 +2968,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>